--- a/important_mails_2026-05-29.xlsx
+++ b/important_mails_2026-05-29.xlsx
@@ -2285,7 +2285,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2300,69 +2300,21 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Fri, 22 May 2026 17:10:56 +0000</t>
+          <t>Sat, 23 May 2026 04:06:08 +0000</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Worten Marketplace - Portugal y España</t>
+          <t>Create FBA removal order by 2026-06-04</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>¡Buenos días!
-Espero que te encuentres bien.
-Mi nombre es Luana Camargo y soy Business Developer en WORTEN Portugal y España, parte de Sonae, uno de los más grandes grupos empresariales en Portugal.
-Te envío este mensaje porque nos gustaría hacer una colaboración entre Weihai EU y el Marketplace de Worten.
-Sobre Worten.
-Somos líderes en el mercado portugués, con 200 tiendas alcanzamos más de 1.2 billones de euros en ventas, de los cuales el 20% vienen del online.
-En Portugal, Worten.pt es el sitio de comercio electrónico más visitado y con mejor desempeño, recibimos más visitas que los principales marketplaces del mundo, los que consideramos nuestra competencia. En compras online, el sitio web de Worten tiene el mayor tráfico de Portugal, más de 10 millones de visitas al mes.
-Es en www.worten.pt y www.worten.es donde puedes mirar nuestro Marketplace.
-Con más de 30 categorías, el Marketplace de Worten quiere ser la plataforma donde los clientes pueden encontrar todo lo que necesitan.
-Con la gran demanda que sentimos, tenemos la oportunidad de aumentar nuestra gama de productos, ¡y trabajar con las mejores empresas es nuestra prioridad !
-Worten Marketplace tiene una estrategia B2C, c</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 23 May 2026 04:06:08 +0000</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-06-04</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2385,39 +2337,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 03:17:21 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2441,39 +2393,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 02:44:04 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (y8kVKdPDvp)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2493,39 +2445,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:33:15 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $105.47 in an attempt to settle your Amazon seller account balance.
@@ -2541,39 +2493,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 02:39:33 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (ZazNpo+O9J)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2599,39 +2551,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 02:56:06 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2647,39 +2599,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2704,39 +2656,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 05:42:00 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (zl4CmeMn1C)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2756,39 +2708,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2808,39 +2760,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2860,39 +2812,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2913,39 +2865,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 13:03:07 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2604121A02)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2965,39 +2917,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3017,39 +2969,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
@@ -3065,39 +3017,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 07:28:26 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (5NT+O11io4)</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3117,39 +3069,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:30:35 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3169,39 +3121,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:29:45 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3218,39 +3170,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:22:00 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3270,39 +3222,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:11 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3322,39 +3274,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:21:19 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -3371,39 +3323,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:07:05 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January-March 2026</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -3420,39 +3372,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 14:48:57 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3472,39 +3424,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:42 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -3528,39 +3480,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:19 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -3584,39 +3536,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 13:46:45 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3636,39 +3588,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:49:45 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3688,39 +3640,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:47:51 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3740,39 +3692,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:36:52 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3792,39 +3744,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:51:22 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3840,39 +3792,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:50:04 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3889,39 +3841,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:49:55 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3941,39 +3893,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:53:51 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -3990,39 +3942,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4039,39 +3991,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4091,39 +4043,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4143,39 +4095,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4192,39 +4144,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
@@ -4239,39 +4191,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:45:41 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -4287,39 +4239,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:23:38 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4339,39 +4291,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4391,39 +4343,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4440,39 +4392,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4492,39 +4444,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4544,39 +4496,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:11:27 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4595,40 +4547,40 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:24:17 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4644,40 +4596,40 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:03:38 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4691,40 +4643,40 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:02:28 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4738,40 +4690,40 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:07:57 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Hello,
 We have reviewed your appeal request. We are rejecting your appeal because the detail page has an image of a child playing with the product. We request you take the following action:
@@ -4784,39 +4736,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 03:03:13 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -4836,39 +4788,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 07:42:16 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-de@amazon.com" &lt;fba-3p-buyability-improvement-de@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -4893,39 +4845,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 10:44:21 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-it@amazon.com" &lt;fba-3p-buyability-improvement-it@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -4950,40 +4902,40 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4998,40 +4950,40 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5045,40 +4997,40 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5092,41 +5044,41 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -5137,39 +5089,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -5188,39 +5140,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -5244,39 +5196,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5294,39 +5246,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5344,39 +5296,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 13:15:01 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5394,39 +5346,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:13:49 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5444,39 +5396,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:19:29 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5494,39 +5446,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 12:52:07 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -5542,39 +5494,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5592,39 +5544,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5642,39 +5594,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -5684,39 +5636,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -5734,6 +5686,54 @@
 To contact us again about this issue, please use the Contact Us form in Seller Central using the following link:
 https://sellercentral-europe.amazon.com/cu/case-dashboard/view-case?caseID=12309992722
 Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 22 May 2026 17:10:56 +0000</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Worten Marketplace - Portugal y España</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>¡Buenos días!
+Espero que te encuentres bien.
+Mi nombre es Luana Camargo y soy Business Developer en WORTEN Portugal y España, parte de Sonae, uno de los más grandes grupos empresariales en Portugal.
+Te envío este mensaje porque nos gustaría hacer una colaboración entre Weihai EU y el Marketplace de Worten.
+Sobre Worten.
+Somos líderes en el mercado portugués, con 200 tiendas alcanzamos más de 1.2 billones de euros en ventas, de los cuales el 20% vienen del online.
+En Portugal, Worten.pt es el sitio de comercio electrónico más visitado y con mejor desempeño, recibimos más visitas que los principales marketplaces del mundo, los que consideramos nuestra competencia. En compras online, el sitio web de Worten tiene el mayor tráfico de Portugal, más de 10 millones de visitas al mes.
+Es en www.worten.pt y www.worten.es donde puedes mirar nuestro Marketplace.
+Con más de 30 categorías, el Marketplace de Worten quiere ser la plataforma donde los clientes pueden encontrar todo lo que necesitan.
+Con la gran demanda que sentimos, tenemos la oportunidad de aumentar nuestra gama de productos, ¡y trabajar con las mejores empresas es nuestra prioridad !
+Worten Marketplace tiene una estrategia B2C, c</t>
         </is>
       </c>
     </row>
